--- a/public/templates/template_siswa.xlsx
+++ b/public/templates/template_siswa.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11008"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yasin/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D9F1CBC-7173-4240-B868-A9786C03D2BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2649D85-B472-624A-B9C5-7A700CBCAA53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Dummy Students" sheetId="1" r:id="rId1"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" forceFullCalc="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
   <si>
     <t>Nama Lengkap</t>
   </si>
@@ -40,7 +40,7 @@
     <t>NISN</t>
   </si>
   <si>
-    <t>Jenis Kelamin</t>
+    <t>Jenis Kelamin (L/P)</t>
   </si>
   <si>
     <t>Tanggal Lahir</t>
@@ -52,41 +52,36 @@
     <t>NIK</t>
   </si>
   <si>
-    <t>Ahmad Fauzan</t>
-  </si>
-  <si>
-    <t>1000000001</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>2012-01-10</t>
-  </si>
-  <si>
-    <t>Jl. Cendana No. 1</t>
-  </si>
-  <si>
-    <t>6472011001120001</t>
+    <t>Tempat Lahir</t>
+  </si>
+  <si>
+    <t>Nama Orang Tua / Wali</t>
+  </si>
+  <si>
+    <t>NIK Orang Tua / Wali</t>
+  </si>
+  <si>
+    <t>No HP Orang Tua / Wali</t>
+  </si>
+  <si>
+    <t>2017-11-16T00:00:00.000000Z</t>
+  </si>
+  <si>
+    <t>CONTOH</t>
+  </si>
+  <si>
+    <t>L/P</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -109,15 +104,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -204,6 +198,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -238,6 +233,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -414,57 +410,87 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="21" customWidth="1"/>
+    <col min="1" max="1" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="49.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
+        <v>11</v>
+      </c>
+      <c r="B2">
+        <v>1234567890</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2">
+        <v>1234567891234560</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>